--- a/project/excel/spdx.xlsx
+++ b/project/excel/spdx.xlsx
@@ -7,59 +7,61 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AIPackage" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="EnergyConsumption" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EnergyConsumptionDescription" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Build" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Annotation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Bundle" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CreationInfo" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DictionaryEntry" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ExternalIdentifier" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ExternalMap" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ExternalRef" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Hash" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="IndividualElement" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="LifecycleScopedRelationship" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="NamespaceMap" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Organization" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="PackageVerificationCode" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Person" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="PositiveIntegerRange" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Relationship" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="SoftwareAgent" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="SpdxDocument" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Tool" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="DatasetPackage" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="ConjunctiveLicenseSet" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="CustomLicense" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="CustomLicenseAddition" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="DisjunctiveLicenseSet" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="IndividualLicensingInfo" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="ListedLicense" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="ListedLicenseException" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="OrLaterOperator" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="WithAdditionOperator" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="CdxPropertiesExtension" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="CdxPropertyEntry" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="CvssV2VulnAssessmentRelationship" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="CvssV3VulnAssessmentRelationship" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="CvssV4VulnAssessmentRelationship" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="EpssVulnAssessmentRelationship" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="ExploitCatalogVulnAssessmentRelationship" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="SsvcVulnAssessmentRelationship" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="VexAffectedVulnAssessmentRelationship" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="VexFixedVulnAssessmentRelationship" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="VexNotAffectedVulnAssessmentRelationship" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="VexUnderInvestigationVulnAssessmentRelationship" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="Vulnerability" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="LicenseExpression" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="SimpleLicensingText" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="ContentIdentifier" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="File" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="Package" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="Sbom" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="Snippet" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="Agent" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Annotation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Bom" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Bundle" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CreationInfo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DictionaryEntry" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ExternalIdentifier" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ExternalMap" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ExternalRef" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Hash" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="IndividualElement" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="LifecycleScopedRelationship" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="NamespaceMap" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Organization" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="PackageVerificationCode" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Person" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="PositiveIntegerRange" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Relationship" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SoftwareAgent" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SpdxDocument" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Tool" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Build" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="CdxPropertiesExtension" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="CdxPropertyEntry" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="LicenseExpression" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="SimpleLicensingText" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="ContentIdentifier" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="File" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Package" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Sbom" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Snippet" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="AIPackage" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="EnergyConsumption" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="EnergyConsumptionDescription" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="DatasetPackage" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="ConjunctiveLicenseSet" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="CustomLicense" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="CustomLicenseAddition" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="DisjunctiveLicenseSet" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="IndividualLicensingInfo" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="ListedLicense" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="ListedLicenseException" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="OrLaterOperator" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="WithAdditionOperator" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="CvssV2VulnAssessmentRela_c5a61d" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="CvssV3VulnAssessmentRela_00cbc1" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="CvssV4VulnAssessmentRela_58d641" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="EpssVulnAssessmentRelationship" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="ExploitCatalogVulnAssess_3782db" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="SsvcVulnAssessmentRelationship" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="VexAffectedVulnAssessmen_00709b" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="VexFixedVulnAssessmentRe_20f2b1" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="VexNotAffectedVulnAssess_f627e5" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="VexUnderInvestigationVul_8b9815" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="Vulnerability" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,231 +467,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>informationAboutTraining</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>modelDataPreprocessing</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>typeOfModel</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>safetyRiskAssessment</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>metricDecisionThreshold</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>useSensitivePersonalInformation</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>energyConsumption</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>limitation</t>
+          <t>externalIdentifier</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>hyperparameter</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>autonomyType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>domain</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>modelExplainability</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>informationAboutApplication</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>standardCompliance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>sourceInfo</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>homePage</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>downloadLocation</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>packageVersion</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>packageUrl</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>attributionText</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>primaryPurpose</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>additionalPurpose</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>contentIdentifier</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>copyrightText</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>standardName</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>builtTime</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>validUntilTime</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>supportLevel</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>suppliedBy</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>originatedBy</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>releaseTime</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>externalIdentifier</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"high,low,medium,serious"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"no,noAssertion,yes"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"no,noAssertion,yes"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -706,26 +544,31 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>definingArtifact</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>locationHint</t>
+          <t>hashValue</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>externalSpdxId</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>verifiedUsing</t>
+          <t>comment</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"adler32,blake2b256,blake2b384,blake2b512,blake3,crystalsDilithium,crystalsKyber,falcon,md2,md4,md5,md6,other,sha1,sha224,sha256,sha384,sha3_224,sha3_256,sha3_384,sha3_512,sha512"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -736,28 +579,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>core_locator</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>externalRefType</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>contentType</t>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>externalIdentifier</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>summary</t>
         </is>
       </c>
     </row>
@@ -772,27 +650,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>hashValue</t>
+          <t>completeness</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>endTime</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>relationshipType</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>startTime</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>comment</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>externalIdentifier</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>summary</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"build,design,development,other,runtime,test"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -803,53 +764,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>externalIdentifier</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>namespace</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>summary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
+          <t>prefix</t>
         </is>
       </c>
     </row>
@@ -864,43 +795,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>scope</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>relationshipType</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>endTime</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -910,51 +841,21 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -965,22 +866,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>prefix</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>namespace</t>
+          <t>hashValue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>packageVerificationCodeExcludedFile</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"adler32,blake2b256,blake2b384,blake2b512,blake3,crystalsDilithium,crystalsKyber,falcon,md2,md4,md5,md6,other,sha1,sha224,sha256,sha384,sha3_224,sha3_256,sha3_384,sha3_512,sha512"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -991,53 +912,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
@@ -1052,28 +983,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>packageVerificationCodeExcludedFile</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>hashValue</t>
+          <t>beginIntegerRange</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>algorithm</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>comment</t>
+          <t>endIntegerRange</t>
         </is>
       </c>
     </row>
@@ -1088,57 +1014,102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>endTime</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>relationshipType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>startTime</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1149,18 +1120,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>endIntegerRange</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>beginIntegerRange</t>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>externalIdentifier</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>summary</t>
         </is>
       </c>
     </row>
@@ -1175,27 +1191,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>finetuningEnergyConsumption</t>
+          <t>contentType</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>inferenceEnergyConsumption</t>
+          <t>annotationType</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>trainingEnergyConsumption</t>
+          <t>statement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>externalIdentifier</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>summary</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"other,review"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1206,90 +1287,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>dataLicense</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>namespaceMap</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>relationshipType</t>
+          <t>element</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>profileConformance</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>endTime</t>
+          <t>rootElement</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ai,build,core,dataset,expandedLicensing,extension,lite,security,simpleLicensing,software"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1302,53 +1393,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
@@ -1363,92 +1464,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>namespaceMap</t>
+          <t>buildEndTime</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>dataLicense</t>
+          <t>buildId</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>buildStartTime</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>buildType</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>profileConformance</t>
+          <t>configSourceDigest</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>rootElement</t>
+          <t>configSourceEntrypoint</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>configSourceUri</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ai,build,core,dataset,expandedLicensing,extension,lite,security,simpleLicensing,software"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1459,53 +1580,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>externalIdentifier</t>
+          <t>cdxProperty</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>summary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
+          <t>type</t>
         </is>
       </c>
     </row>
@@ -1520,221 +1606,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>datasetSize</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>datasetType</t>
+          <t>cdxPropName</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>anonymizationMethodUsed</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>datasetUpdateMechanism</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>dataCollectionProcess</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>knownBias</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>sensor</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>dataPreprocessing</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>intendedUse</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>confidentialityLevel</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>datasetAvailability</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>hasSensitivePersonalInformation</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>datasetNoise</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>sourceInfo</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>homePage</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>downloadLocation</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>packageVersion</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>packageUrl</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>attributionText</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>primaryPurpose</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>additionalPurpose</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>contentIdentifier</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>copyrightText</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>standardName</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>builtTime</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>validUntilTime</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>supportLevel</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>suppliedBy</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>originatedBy</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>releaseTime</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>externalIdentifier</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>summary</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
+          <t>cdxPropValue</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"amber,clear,green,red"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"clickthrough,directDownload,query,registration,scrapingScript"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"no,noAssertion,yes"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AA2:AA1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1745,58 +1637,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>member</t>
+          <t>customIdToUri</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>licenseExpression</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>licenseListVersion</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
@@ -1811,98 +1723,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>obsoletedBy</t>
+          <t>licenseText</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>standardLicenseHeader</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>seeAlso</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>isFsfLibre</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>isDeprecatedLicenseId</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>isOsiApproved</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>licenseXml</t>
+          <t>description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>licenseText</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>standardLicenseTemplate</t>
+          <t>externalIdentifier</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>externalIdentifier</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
@@ -1917,87 +1799,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>standardAdditionTemplate</t>
+          <t>contentIdentifierType</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>seeAlso</t>
+          <t>contentIdentifierValue</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>obsoletedBy</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>licenseXml</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>isDeprecatedAdditionId</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>additionText</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>externalIdentifier</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>summary</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
           <t>comment</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"gitoid,swhid"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2008,62 +1840,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>member</t>
+          <t>contentType</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>fileKind</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>additionalPurpose</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attributionText</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>contentIdentifier</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>copyrightText</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>primaryPurpose</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>builtTime</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>originatedBy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>releaseTime</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>standardName</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>supportLevel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>validUntilTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"directory,file"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2074,57 +1989,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>downloadLocation</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>homePage</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>packageUrl</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>packageVersion</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sourceInfo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>additionalPurpose</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>attributionText</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>contentIdentifier</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>copyrightText</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>primaryPurpose</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>builtTime</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>originatedBy</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>releaseTime</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>standardName</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>supportLevel</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>validUntilTime</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2135,22 +2150,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>energyQuantity</t>
+          <t>context</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>energyUnit</t>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>profileConformance</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rootElement</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>externalIdentifier</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>summary</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ai,build,core,dataset,expandedLicensing,extension,lite,security,simpleLicensing,software"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2161,112 +2246,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>deprecatedVersion</t>
+          <t>sbomType</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>listVersionAdded</t>
+          <t>context</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>obsoletedBy</t>
+          <t>element</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>standardLicenseHeader</t>
+          <t>profileConformance</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>seeAlso</t>
+          <t>rootElement</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>isFsfLibre</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>isDeprecatedLicenseId</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>isOsiApproved</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>licenseXml</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>licenseText</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>standardLicenseTemplate</t>
+          <t>description</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"analyzed,build,deployed,design,runtime,source"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ai,build,core,dataset,expandedLicensing,extension,lite,security,simpleLicensing,software"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2277,97 +2350,147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>listVersionAdded</t>
+          <t>byteRange</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>deprecatedVersion</t>
+          <t>lineRange</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>standardAdditionTemplate</t>
+          <t>snippetFromFile</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>seeAlso</t>
+          <t>additionalPurpose</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>obsoletedBy</t>
+          <t>attributionText</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>licenseXml</t>
+          <t>contentIdentifier</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>isDeprecatedAdditionId</t>
+          <t>copyrightText</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>additionText</t>
+          <t>primaryPurpose</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>builtTime</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>originatedBy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>releaseTime</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>standardName</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>supportLevel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>validUntilTime</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2378,62 +2501,241 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:AQ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>subjectLicense</t>
+          <t>autonomyType</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>energyConsumption</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>hyperparameter</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>informationAboutApplication</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>informationAboutTraining</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>limitation</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>metricDecisionThreshold</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>modelDataPreprocessing</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>modelExplainability</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>safetyRiskAssessment</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>standardCompliance</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>typeOfModel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>useSensitivePersonalInformation</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>downloadLocation</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>homePage</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>packageUrl</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>packageVersion</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>sourceInfo</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>additionalPurpose</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>attributionText</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>contentIdentifier</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>copyrightText</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>primaryPurpose</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>builtTime</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>originatedBy</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>releaseTime</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>standardName</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>supportLevel</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>validUntilTime</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"no,noAssertion,yes"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"high,low,medium,serious"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"no,noAssertion,yes"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AE2:AE1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2444,63 +2746,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>subjectExtendableLicense</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>subjectAddition</t>
+          <t>finetuningEnergyConsumption</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>externalIdentifier</t>
+          <t>inferenceEnergyConsumption</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>summary</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
+          <t>trainingEnergyConsumption</t>
         </is>
       </c>
     </row>
@@ -2515,17 +2782,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>cdxProperty</t>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>energyQuantity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>energyUnit</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kilowattHour,megajoule,other"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2536,22 +2818,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>cdxPropValue</t>
+          <t>anonymizationMethodUsed</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>cdxPropName</t>
+          <t>confidentialityLevel</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dataCollectionProcess</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>dataPreprocessing</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>datasetAvailability</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>datasetNoise</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>datasetSize</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>datasetType</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>datasetUpdateMechanism</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>hasSensitivePersonalInformation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>intendedUse</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>knownBias</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>sensor</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>downloadLocation</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>homePage</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>packageUrl</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>packageVersion</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>sourceInfo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>additionalPurpose</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>attributionText</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>contentIdentifier</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>copyrightText</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>primaryPurpose</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>builtTime</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>originatedBy</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>releaseTime</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>standardName</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>supportLevel</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>validUntilTime</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>externalIdentifier</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>summary</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"amber,clear,green,red"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"clickthrough,directDownload,query,registration,scrapingScript"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"audio,categorical,graph,image,noAssertion,numeric,other,sensor,structured,syntactic,text,timeseries,timestamp,video"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"no,noAssertion,yes"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2562,127 +3056,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>vectorString</t>
+          <t>member</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>withdrawnTime</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>publishedTime</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>assessedElement</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>modifiedTime</t>
+          <t>description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>externalIdentifier</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>relationshipType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>endTime</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>externalIdentifier</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2693,135 +3132,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>licenseText</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>vectorString</t>
+          <t>licenseXml</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>obsoletedBy</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>withdrawnTime</t>
+          <t>seeAlso</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>publishedTime</t>
+          <t>isDeprecatedLicenseId</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>assessedElement</t>
+          <t>isFsfLibre</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>isOsiApproved</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>modifiedTime</t>
+          <t>standardLicenseHeader</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>standardLicenseTemplate</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>type</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>relationshipType</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>endTime</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"critical,high,low,medium,none"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2832,135 +3248,97 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>licenseXml</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>vectorString</t>
+          <t>obsoletedBy</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>seeAlso</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>withdrawnTime</t>
+          <t>additionText</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>publishedTime</t>
+          <t>isDeprecatedAdditionId</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>assessedElement</t>
+          <t>standardAdditionTemplate</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>type</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>modifiedTime</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>relationshipType</t>
+          <t>description</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>endTime</t>
+          <t>externalIdentifier</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>externalIdentifier</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>name</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"critical,high,low,medium,none"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2971,127 +3349,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>percentile</t>
+          <t>member</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>withdrawnTime</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>publishedTime</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>assessedElement</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>modifiedTime</t>
+          <t>description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>externalIdentifier</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>relationshipType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>endTime</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>externalIdentifier</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3102,102 +3425,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>buildType</t>
+          <t>context</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>buildEndTime</t>
+          <t>element</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>buildId</t>
+          <t>profileConformance</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>configSourceDigest</t>
+          <t>rootElement</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>buildStartTime</t>
+          <t>type</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>configSourceUri</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>configSourceEntrypoint</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ai,build,core,dataset,expandedLicensing,extension,lite,security,simpleLicensing,software"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3208,132 +3521,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>exploited</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>security_locator</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>catalogType</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>withdrawnTime</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>publishedTime</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>assessedElement</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>modifiedTime</t>
+          <t>externalIdentifier</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>startTime</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>relationshipType</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>endTime</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>externalIdentifier</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3344,125 +3592,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>decisionType</t>
+          <t>deprecatedVersion</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>withdrawnTime</t>
+          <t>listVersionAdded</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>publishedTime</t>
+          <t>licenseText</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>assessedElement</t>
+          <t>licenseXml</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>obsoletedBy</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>modifiedTime</t>
+          <t>seeAlso</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>isDeprecatedLicenseId</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>isFsfLibre</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>isOsiApproved</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>relationshipType</t>
+          <t>standardLicenseHeader</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>standardLicenseTemplate</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>endTime</t>
+          <t>type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"act,attend,track,trackStar"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3473,83 +3718,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>actionStatement</t>
+          <t>deprecatedVersion</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>actionStatementTime</t>
+          <t>listVersionAdded</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>vexVersion</t>
+          <t>licenseXml</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>statusNotes</t>
+          <t>obsoletedBy</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>withdrawnTime</t>
+          <t>seeAlso</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>publishedTime</t>
+          <t>additionText</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>assessedElement</t>
+          <t>isDeprecatedAdditionId</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>standardAdditionTemplate</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>modifiedTime</t>
+          <t>type</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>relationshipType</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>description</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>endTime</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
@@ -3559,51 +3804,21 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3614,127 +3829,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>vexVersion</t>
+          <t>subjectLicense</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>statusNotes</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>withdrawnTime</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>publishedTime</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>assessedElement</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>modifiedTime</t>
+          <t>description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>externalIdentifier</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>startTime</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>relationshipType</t>
+          <t>name</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>endTime</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>externalIdentifier</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3745,145 +3905,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>impactStatementTime</t>
+          <t>subjectAddition</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>justificationType</t>
+          <t>subjectExtendableLicense</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>impactStatement</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>vexVersion</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>statusNotes</t>
+          <t>verifiedUsing</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>withdrawnTime</t>
+          <t>spdxId</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>publishedTime</t>
+          <t>creationInfo</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>assessedElement</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>modifiedTime</t>
+          <t>externalIdentifier</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>externalRef</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>completeness</t>
+          <t>name</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>startTime</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>relationshipType</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>endTime</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>externalIdentifier</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"componentNotPresent,inlineMitigationsAlreadyExist,vulnerableCodeCannotBeControlledByAdversary,vulnerableCodeNotInExecutePath,vulnerableCodeNotPresent"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"complete,incomplete,noAssertion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3894,124 +3986,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>vexVersion</t>
+          <t>score</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>statusNotes</t>
+          <t>vectorString</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>modifiedTime</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publishedTime</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>withdrawnTime</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>publishedTime</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>assessedElement</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>suppliedBy</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>modifiedTime</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>endTime</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>relationshipType</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>startTime</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>to</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>completeness</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>startTime</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>relationshipType</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>endTime</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"complete,incomplete,noAssertion"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4025,110 +4127,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>vectorString</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>modifiedTime</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>publishedTime</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>withdrawnTime</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>modifiedTime</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>publishedTime</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>standardName</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>builtTime</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>validUntilTime</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>supportLevel</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>assessedElement</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>originatedBy</t>
+          <t>completeness</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>releaseTime</t>
+          <t>endTime</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>relationshipType</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>startTime</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"critical,high,low,medium,none"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4141,72 +4276,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>customIdToUri</t>
+          <t>score</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>licenseExpression</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>licenseListVersion</t>
+          <t>vectorString</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>modifiedTime</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>publishedTime</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>withdrawnTime</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>assessedElement</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>endTime</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>relationshipType</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>startTime</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"critical,high,low,medium,none"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4217,62 +4425,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>licenseText</t>
+          <t>percentile</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>modifiedTime</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publishedTime</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>withdrawnTime</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>assessedElement</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>endTime</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>relationshipType</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>startTime</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4283,30 +4566,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>contentIdentifierValue</t>
+          <t>catalogType</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>contentIdentifierType</t>
+          <t>exploited</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>security_locator</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>modifiedTime</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>publishedTime</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>withdrawnTime</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>assessedElement</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>endTime</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>relationshipType</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>startTime</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>comment</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>externalIdentifier</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>summary</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"gitoid,swhid"</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"kev,other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4319,73 +4715,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>contentType</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>created</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>annotationType</t>
+          <t>createdBy</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>externalIdentifier</t>
+          <t>createdUsing</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>summary</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
+          <t>specVersion</t>
         </is>
       </c>
     </row>
@@ -4406,127 +4767,127 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>fileKind</t>
+          <t>decisionType</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>contentType</t>
+          <t>modifiedTime</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>attributionText</t>
+          <t>publishedTime</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>primaryPurpose</t>
+          <t>suppliedBy</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>additionalPurpose</t>
+          <t>withdrawnTime</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>contentIdentifier</t>
+          <t>assessedElement</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>copyrightText</t>
+          <t>completeness</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>standardName</t>
+          <t>endTime</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>builtTime</t>
+          <t>from</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>validUntilTime</t>
+          <t>relationshipType</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>supportLevel</t>
+          <t>startTime</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>to</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>originatedBy</t>
+          <t>type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>releaseTime</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"directory,file"</formula1>
+      <formula1>"act,attend,track,trackStar"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4545,139 +4906,139 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>sourceInfo</t>
+          <t>actionStatement</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>homePage</t>
+          <t>actionStatementTime</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>downloadLocation</t>
+          <t>statusNotes</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>packageVersion</t>
+          <t>vexVersion</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>packageUrl</t>
+          <t>modifiedTime</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>attributionText</t>
+          <t>publishedTime</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>primaryPurpose</t>
+          <t>suppliedBy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>additionalPurpose</t>
+          <t>withdrawnTime</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>contentIdentifier</t>
+          <t>assessedElement</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>copyrightText</t>
+          <t>completeness</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>standardName</t>
+          <t>endTime</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>builtTime</t>
+          <t>from</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>validUntilTime</t>
+          <t>relationshipType</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>supportLevel</t>
+          <t>startTime</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>to</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>originatedBy</t>
+          <t>type</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>releaseTime</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4690,88 +5051,135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>sbomType</t>
+          <t>statusNotes</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>vexVersion</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>modifiedTime</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>profileConformance</t>
+          <t>publishedTime</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>rootElement</t>
+          <t>suppliedBy</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>withdrawnTime</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>assessedElement</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>endTime</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>relationshipType</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>startTime</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"analyzed,build,deployed,design,runtime,source"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ai,build,core,dataset,expandedLicensing,extension,lite,security,simpleLicensing,software"</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4784,134 +5192,419 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>impactStatement</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>impactStatementTime</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>justificationType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>statusNotes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>vexVersion</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>modifiedTime</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>publishedTime</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>withdrawnTime</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>assessedElement</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>endTime</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>relationshipType</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>startTime</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>externalIdentifier</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"componentNotPresent,inlineMitigationsAlreadyExist,vulnerableCodeCannotBeControlledByAdversary,vulnerableCodeNotInExecutePath,vulnerableCodeNotPresent"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lineRange</t>
+          <t>statusNotes</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>snippetFromFile</t>
+          <t>vexVersion</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>byteRange</t>
+          <t>modifiedTime</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>attributionText</t>
+          <t>publishedTime</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>primaryPurpose</t>
+          <t>suppliedBy</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>additionalPurpose</t>
+          <t>withdrawnTime</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>contentIdentifier</t>
+          <t>assessedElement</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>copyrightText</t>
+          <t>completeness</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>standardName</t>
+          <t>endTime</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>builtTime</t>
+          <t>from</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>validUntilTime</t>
+          <t>relationshipType</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>supportLevel</t>
+          <t>startTime</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>suppliedBy</t>
+          <t>to</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>originatedBy</t>
+          <t>type</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>releaseTime</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>externalIdentifier</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>summary</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"complete,incomplete,noAssertion"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>modifiedTime</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>publishedTime</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>withdrawnTime</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>suppliedBy</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>builtTime</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>originatedBy</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>releaseTime</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>standardName</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>supportLevel</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>validUntilTime</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>spdxId</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>creationInfo</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>externalIdentifier</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>externalRef</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"deployed,development,endOfSupport,limitedSupport,noAssertion,noSupport,support"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4925,82 +5618,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>key</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>profileConformance</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>rootElement</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>externalIdentifier</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>summary</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>verifiedUsing</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>externalRef</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>creationInfo</t>
+          <t>value</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ai,build,core,dataset,expandedLicensing,extension,lite,security,simpleLicensing,software"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5011,37 +5649,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>createdBy</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>createdUsing</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>created</t>
+          <t>externalIdentifierType</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>specVersion</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>identifierLocator</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>issuingAuthority</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"cpe22,cpe23,cve,email,gitoid,other,packageUrl,securityOther,swhid,swid,urlScheme"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5052,18 +5700,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>verifiedUsing</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>definingArtifact</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>externalSpdxId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>locationHint</t>
         </is>
       </c>
     </row>
@@ -5084,27 +5747,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>identifierLocator</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>externalIdentifierType</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>issuingAuthority</t>
+          <t>contentType</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>identifier</t>
+          <t>externalRefType</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>locator</t>
         </is>
       </c>
     </row>
